--- a/综合评分.xlsx
+++ b/综合评分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sourceCode\aitest-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0381A89-17F7-4511-801F-D96CE9C34A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3A88EF-5717-4A0E-B2EC-2700D3268B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,32 +25,37 @@
     <t>模型名称</t>
   </si>
   <si>
+    <t>无法满足特定服务类型的安全需求占比数据</t>
+  </si>
+  <si>
+    <t>DeepSeek V3.2</t>
+  </si>
+  <si>
     <t>综合越狱占比数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>违反社会主义核心价值观占比数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>歧视占比数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>商业违法违规占比数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>侵犯他人合法权益占比数据</t>
-  </si>
-  <si>
-    <t>无法满足特定服务类型的安全需求占比数据</t>
-  </si>
-  <si>
-    <t>DeepSeek V3.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -59,22 +64,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF366092"/>
+        <bgColor rgb="FF366092"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -82,12 +108,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -393,62 +446,63 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3">
         <v>0.08</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>0.08</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="3">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>